--- a/Docs/QA-Testing/Test_Case_StateTransition.xlsx
+++ b/Docs/QA-Testing/Test_Case_StateTransition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/QA-Testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD55AF5-3B1F-8044-A702-D80BF8B34373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DCDFEA-075A-AA4A-B9AA-15238D7FB978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="State Transition Test Cases" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="130">
   <si>
     <t>TC ID</t>
   </si>
@@ -106,9 +106,6 @@
     <t>PASS (Blocked)</t>
   </si>
   <si>
-    <t>Bug #10</t>
-  </si>
-  <si>
     <t>Order ID=2147483648, Status=1(FINISHED), Buyer=customer1@email.com</t>
   </si>
   <si>
@@ -187,9 +184,6 @@
     <t>Điều kiện ban đầu</t>
   </si>
   <si>
-    <t>Kết quả mong đượi</t>
-  </si>
-  <si>
     <t>Kết quả thực nhận</t>
   </si>
   <si>
@@ -245,6 +239,180 @@
   </si>
   <si>
     <t>Controller kiểm tra buyerEmail để xác định vai trò khách hàng. Khách hàng không phải là chủ sở hữu sẽ nhận phản hồi 401.</t>
+  </si>
+  <si>
+    <t>SCRUM-59</t>
+  </si>
+  <si>
+    <t>Kết quả mong đợi</t>
+  </si>
+  <si>
+    <t>TC-ST09</t>
+  </si>
+  <si>
+    <t>TC-ST10</t>
+  </si>
+  <si>
+    <t>TC-ST11</t>
+  </si>
+  <si>
+    <t>TC-ST12</t>
+  </si>
+  <si>
+    <t>TC-ST13</t>
+  </si>
+  <si>
+    <t>Bỏ vào giỏ hàng (Phiên Khách hàng chưa đăng nhập)</t>
+  </si>
+  <si>
+    <t>Bỏ vào giỏ hàng (Phiên Khách hàng đã đăng nhập)</t>
+  </si>
+  <si>
+    <t>Đăng nhập với giỏ hàng của khách chưa đăng nhập (Merge giỏ hàng)</t>
+  </si>
+  <si>
+    <t>Checkout với giỏ hàng trống (Blocked)</t>
+  </si>
+  <si>
+    <t>Checkout với item trong giỏ hàng</t>
+  </si>
+  <si>
+    <t>TC-ST14</t>
+  </si>
+  <si>
+    <t>TC-ST15</t>
+  </si>
+  <si>
+    <t>Xóa sản phẩm cuối khỏi giỏ hàng (Pre-empty)</t>
+  </si>
+  <si>
+    <t>Xóa tất cả sản phẩm (Logged-in) trở lại giỏ hàng trống</t>
+  </si>
+  <si>
+    <t>Giỏ hàng trống, chưa đăng nhập (no auth token)</t>
+  </si>
+  <si>
+    <t>Giỏ hàng trống, đã đăng nhập (valid auth token)</t>
+  </si>
+  <si>
+    <t>Có item trong tài khoản guess (chưa đăng nhập như ST-09)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập (valid auth token), số item trong giỏ hàng lớn hơn hoặc bằng 1</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập (valid auth token), Không có item trong giỏ hàng</t>
+  </si>
+  <si>
+    <t>Chưa đăng nhập, item count trong giỏ hàng =1</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập, số sản phẩm trong giỏ hàng lớn hơn hoặc bằng 1</t>
+  </si>
+  <si>
+    <t>Empty -&gt; Guest</t>
+  </si>
+  <si>
+    <t>Empty -&gt; Logged In</t>
+  </si>
+  <si>
+    <t>Guest -&gt; Merge -&gt; Logged In</t>
+  </si>
+  <si>
+    <t>Logged In -&gt; Checkout Done</t>
+  </si>
+  <si>
+    <t>Logged In -&gt; Logged in (Blocked)</t>
+  </si>
+  <si>
+    <t>Guest -&gt; Empty</t>
+  </si>
+  <si>
+    <t>Logged in -&gt; Empty</t>
+  </si>
+  <si>
+    <t>Guest</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Guest -&gt; Customer</t>
+  </si>
+  <si>
+    <t>/api/cart/add</t>
+  </si>
+  <si>
+    <t>/api/user/login</t>
+  </si>
+  <si>
+    <t>/api/cart/checkout</t>
+  </si>
+  <si>
+    <t>/api/cart/remove</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>{"productId: "F001", "count", 2"}</t>
+  </si>
+  <si>
+    <t>{"productId: "F001", "count", 3"}</t>
+  </si>
+  <si>
+    <t>{"email: "customer1@gmail.com", "password": "customer123""}</t>
+  </si>
+  <si>
+    <t>{"productId": "F001"}</t>
+  </si>
+  <si>
+    <t>HTTP 200, Empty cart</t>
+  </si>
+  <si>
+    <t>HTTP 400 Bad Request, "Cart is empty"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 200, </t>
+  </si>
+  <si>
+    <t>HTTP 200, Cart State = guest</t>
+  </si>
+  <si>
+    <t>HTTP 200, Product added to cart (logged user)</t>
+  </si>
+  <si>
+    <t>HTTP 200, Product added to cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 200, Product merged from guest to logged in user </t>
+  </si>
+  <si>
+    <t>HTTP 200, Product merged</t>
+  </si>
+  <si>
+    <t>Khách hàng chưa đăng nhập vẫn có thể bỏ hàng vào giỏ hàng, khi đăng nhập thì sẽ merge từ giỏ hàng khách vào giỏ hàng khách đăng nhập</t>
+  </si>
+  <si>
+    <t>Khách hàng đã đăng nhập thì có thể thêm vào giỏ hàng</t>
+  </si>
+  <si>
+    <t>Tài khoản khách có giỏ hàng, khi đăng nhập vào hệ thống sẽ merge giỏ hàng qua user đã đăng nhập</t>
+  </si>
+  <si>
+    <t>Thanh toán với các món hàng đã cho vào order</t>
+  </si>
+  <si>
+    <t>Không thể thanh toán được vì không có sản phẩm, khi vào order sẽ thể hiện cart is empty, yêu cầu khách hàng tìm đặt sản phẩm</t>
+  </si>
+  <si>
+    <t>Ở người dùng Guest, khi xóa sản phẩm khỏi giỏ hàng thì có thể ra lại trang chủ tìm SP khác</t>
+  </si>
+  <si>
+    <t>Ở người dùng đăng nhập, khi xóa sản phẩm khỏi giỏ hàng thì có thể ra lại trang chủ tìm SP khác</t>
   </si>
 </sst>
 </file>
@@ -279,7 +447,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -304,8 +472,26 @@
         <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -328,11 +514,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -340,14 +537,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -651,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -674,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -695,68 +925,68 @@
         <v>5</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>58</v>
+      <c r="M2" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>62</v>
+      <c r="A3" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
@@ -782,69 +1012,69 @@
       <c r="J3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="51" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>69</v>
+      <c r="L4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="51" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>64</v>
+      <c r="A5" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>19</v>
@@ -864,72 +1094,72 @@
       <c r="J5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>69</v>
+      <c r="L5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="A6" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>70</v>
+      <c r="L6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="34" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>49</v>
+      <c r="A7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>20</v>
@@ -941,77 +1171,77 @@
         <v>12</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>15</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="A8" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="3" t="s">
+      <c r="J8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>72</v>
+      <c r="M8" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>68</v>
+      <c r="A9" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>10</v>
@@ -1023,24 +1253,312 @@
         <v>12</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="8" t="s">
         <v>15</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/Docs/QA-Testing/Test_Case_StateTransition.xlsx
+++ b/Docs/QA-Testing/Test_Case_StateTransition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/QA-Testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UserData\Desktop\sp3\DASUA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DCDFEA-075A-AA4A-B9AA-15238D7FB978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E49E416-2EE9-4EDE-84B4-FFB6EA046892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="State Transition Test Cases" sheetId="1" r:id="rId1"/>
@@ -247,21 +247,6 @@
     <t>Kết quả mong đợi</t>
   </si>
   <si>
-    <t>TC-ST09</t>
-  </si>
-  <si>
-    <t>TC-ST10</t>
-  </si>
-  <si>
-    <t>TC-ST11</t>
-  </si>
-  <si>
-    <t>TC-ST12</t>
-  </si>
-  <si>
-    <t>TC-ST13</t>
-  </si>
-  <si>
     <t>Bỏ vào giỏ hàng (Phiên Khách hàng chưa đăng nhập)</t>
   </si>
   <si>
@@ -277,12 +262,6 @@
     <t>Checkout với item trong giỏ hàng</t>
   </si>
   <si>
-    <t>TC-ST14</t>
-  </si>
-  <si>
-    <t>TC-ST15</t>
-  </si>
-  <si>
     <t>Xóa sản phẩm cuối khỏi giỏ hàng (Pre-empty)</t>
   </si>
   <si>
@@ -413,13 +392,34 @@
   </si>
   <si>
     <t>Ở người dùng đăng nhập, khi xóa sản phẩm khỏi giỏ hàng thì có thể ra lại trang chủ tìm SP khác</t>
+  </si>
+  <si>
+    <t>TC-ST-09</t>
+  </si>
+  <si>
+    <t>TC-ST-10</t>
+  </si>
+  <si>
+    <t>TC-ST-11</t>
+  </si>
+  <si>
+    <t>TC-ST-12</t>
+  </si>
+  <si>
+    <t>TC-ST-13</t>
+  </si>
+  <si>
+    <t>TC-ST-14</t>
+  </si>
+  <si>
+    <t>TC-ST-15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,7 +491,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -514,22 +514,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -540,17 +529,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -558,26 +538,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -882,16 +862,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="30" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="18" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="22" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="10" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="18" customWidth="1" outlineLevel="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="40" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
@@ -899,7 +879,7 @@
     <col min="13" max="13" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="28.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -940,49 +920,49 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:13" ht="28.8">
+      <c r="A2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:13" ht="28.8">
+      <c r="A3" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1012,7 +992,7 @@
       <c r="J3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L3" s="2" t="s">
@@ -1022,49 +1002,49 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="51" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:13" ht="40.200000000000003">
+      <c r="A4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="5" t="s">
         <v>26</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="51" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:13" ht="40.200000000000003">
+      <c r="A5" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1094,62 +1074,62 @@
       <c r="J5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="5" t="s">
         <v>26</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:13" ht="43.2">
+      <c r="A6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="34" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:13" ht="28.8">
+      <c r="A7" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1176,7 +1156,7 @@
       <c r="J7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L7" s="2" t="s">
@@ -1186,49 +1166,49 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
+    <row r="8" spans="1:13" ht="28.8">
+      <c r="A8" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:13" ht="43.2">
+      <c r="A9" s="6" t="s">
         <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1258,7 +1238,7 @@
       <c r="J9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L9" s="2" t="s">
@@ -1268,291 +1248,291 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:13" ht="43.2">
+      <c r="A10" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="28.8">
+      <c r="A11" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="57.6">
+      <c r="A12" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="28.8">
+      <c r="A13" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="43.2">
+      <c r="A14" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.8">
+      <c r="A15" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="C15" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="F15" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="K10" s="8" t="s">
+      <c r="H15" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M10" s="11" t="s">
-        <v>123</v>
+      <c r="M15" s="12" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="13" t="s">
+    <row r="16" spans="1:13" ht="28.8">
+      <c r="A16" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="14" t="s">
+      <c r="C16" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="K11" s="8" t="s">
+      <c r="F16" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M11" s="13" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="64" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="I12" s="12" t="s">
+      <c r="M16" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/QA-Testing/Test_Case_StateTransition.xlsx
+++ b/Docs/QA-Testing/Test_Case_StateTransition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEC7E0F-CFEB-49EF-8B07-EB8D404E5710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0FB3E0-0BFD-4D3A-9E7B-6E787DCE0830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,12 +19,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'State Transition Test Cases'!$A$1:$M$9</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="133">
   <si>
     <t>TC ID</t>
   </si>
@@ -420,6 +419,9 @@
   </si>
   <si>
     <t>SCRUM-78</t>
+  </si>
+  <si>
+    <t>200 OK</t>
   </si>
 </sst>
 </file>
@@ -1466,7 +1468,7 @@
         <v>105</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>40</v>

--- a/Docs/QA-Testing/Test_Case_StateTransition.xlsx
+++ b/Docs/QA-Testing/Test_Case_StateTransition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0FB3E0-0BFD-4D3A-9E7B-6E787DCE0830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B95E15-8307-495E-95FF-BF404E090F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="State Transition Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'State Transition Test Cases'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'State Transition Test Cases'!$A$1:$N$9</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="131">
   <si>
     <t>TC ID</t>
   </si>
@@ -142,9 +142,6 @@
     <t>HTTP 400 + ORDER_STATUS_ERROR, status unchanged</t>
   </si>
   <si>
-    <t>HTTP 500 'Status is not correct' (code finish(): status!=NEW -&gt; MyException, no handler -&gt; 500)</t>
-  </si>
-  <si>
     <t>FAIL</t>
   </si>
   <si>
@@ -166,9 +163,6 @@
     <t>FINISHED(1) → CANCELED(2) [BLOCKED]</t>
   </si>
   <si>
-    <t>HTTP 500 'Status is not correct' (code cancel(): status!=NEW -&gt; MyException, no handler -&gt; 500)</t>
-  </si>
-  <si>
     <t>Business State đúng (chặn chuyển trạng thái) nhưng API Response sai: code ném MyException(ORDER_STATUS_ERROR) không có handler =&gt; trả 500 thay vì 400.</t>
   </si>
   <si>
@@ -190,9 +184,6 @@
     <t>1st: HTTP 200 + status=2; 2nd: HTTP 400 + ORDER_STATUS_ERROR</t>
   </si>
   <si>
-    <t>1st: HTTP 200, status=2; 2nd: HTTP 500 'Status is not correct'</t>
-  </si>
-  <si>
     <t>Idempotency đúng (lệnh hủy thứ 2 bị chặn) nhưng API Response 2nd sai: trả 500 thay vì 400 + ORDER_STATUS_ERROR.</t>
   </si>
   <si>
@@ -421,7 +412,10 @@
     <t>SCRUM-78</t>
   </si>
   <si>
-    <t>200 OK</t>
+    <t>400 (lần 2)</t>
+  </si>
+  <si>
+    <t>Retest</t>
   </si>
 </sst>
 </file>
@@ -888,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -903,10 +897,11 @@
     <col min="10" max="10" width="40" customWidth="1"/>
     <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="44.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" customWidth="1"/>
+    <col min="14" max="14" width="44.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -944,10 +939,13 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>13</v>
       </c>
@@ -984,11 +982,14 @@
       <c r="L2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
@@ -1025,11 +1026,14 @@
       <c r="L3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="53.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>34</v>
       </c>
@@ -1057,31 +1061,34 @@
       <c r="I4" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="13">
+        <v>400</v>
+      </c>
+      <c r="K4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="L4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M4" s="14" t="s">
+    </row>
+    <row r="5" spans="1:14" ht="53.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="53.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>30</v>
@@ -1098,31 +1105,34 @@
       <c r="I5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="13">
+        <v>400</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="6" t="s">
+      <c r="B6" s="13" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="D6" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>52</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>17</v>
@@ -1131,42 +1141,45 @@
         <v>18</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="B7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" s="13" t="s">
+      <c r="C7" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>31</v>
@@ -1178,10 +1191,10 @@
         <v>20</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>23</v>
@@ -1189,25 +1202,28 @@
       <c r="L7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="4" t="s">
-        <v>128</v>
+      <c r="M7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>18</v>
@@ -1219,10 +1235,10 @@
         <v>20</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>23</v>
@@ -1230,25 +1246,28 @@
       <c r="L8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>18</v>
@@ -1260,10 +1279,10 @@
         <v>20</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>23</v>
@@ -1271,40 +1290,43 @@
       <c r="L9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="F10" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>78</v>
-      </c>
       <c r="H10" s="8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>23</v>
@@ -1312,40 +1334,43 @@
       <c r="L10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="8" t="s">
-        <v>130</v>
+      <c r="M10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="E11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="J11" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>84</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>23</v>
@@ -1353,40 +1378,43 @@
       <c r="L11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="M11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="F12" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="J12" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>23</v>
@@ -1394,40 +1422,43 @@
       <c r="L12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="E13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="I13" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="J13" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>23</v>
@@ -1435,79 +1466,85 @@
       <c r="L13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>100</v>
       </c>
+      <c r="D14" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" s="8">
+        <v>400</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>103</v>
+      </c>
     </row>
-    <row r="14" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="8" t="s">
+    <row r="15" spans="1:14" ht="69" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I14" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="M14" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="69" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>110</v>
-      </c>
       <c r="E15" s="10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>23</v>
@@ -1515,38 +1552,41 @@
       <c r="L15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="M15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>116</v>
-      </c>
       <c r="E16" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H16" s="8"/>
       <c r="I16" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>23</v>
@@ -1554,12 +1594,15 @@
       <c r="L16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M16" s="8" t="s">
-        <v>117</v>
+      <c r="M16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:N9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>

--- a/Docs/QA-Testing/Test_Case_StateTransition.xlsx
+++ b/Docs/QA-Testing/Test_Case_StateTransition.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/QA-Testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B95E15-8307-495E-95FF-BF404E090F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97960FBD-34D8-DD47-B99E-E3585D9D365D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="State Transition Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'State Transition Test Cases'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'State Transition Test Cases'!$A$1:$M$9</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="137">
   <si>
     <t>TC ID</t>
   </si>
@@ -142,6 +142,9 @@
     <t>HTTP 400 + ORDER_STATUS_ERROR, status unchanged</t>
   </si>
   <si>
+    <t>HTTP 500 'Status is not correct' (code finish(): status!=NEW -&gt; MyException, no handler -&gt; 500)</t>
+  </si>
+  <si>
     <t>FAIL</t>
   </si>
   <si>
@@ -163,6 +166,9 @@
     <t>FINISHED(1) → CANCELED(2) [BLOCKED]</t>
   </si>
   <si>
+    <t>HTTP 500 'Status is not correct' (code cancel(): status!=NEW -&gt; MyException, no handler -&gt; 500)</t>
+  </si>
+  <si>
     <t>Business State đúng (chặn chuyển trạng thái) nhưng API Response sai: code ném MyException(ORDER_STATUS_ERROR) không có handler =&gt; trả 500 thay vì 400.</t>
   </si>
   <si>
@@ -184,6 +190,9 @@
     <t>1st: HTTP 200 + status=2; 2nd: HTTP 400 + ORDER_STATUS_ERROR</t>
   </si>
   <si>
+    <t>1st: HTTP 200, status=2; 2nd: HTTP 500 'Status is not correct'</t>
+  </si>
+  <si>
     <t>Idempotency đúng (lệnh hủy thứ 2 bị chặn) nhưng API Response 2nd sai: trả 500 thay vì 400 + ORDER_STATUS_ERROR.</t>
   </si>
   <si>
@@ -412,10 +421,19 @@
     <t>SCRUM-78</t>
   </si>
   <si>
-    <t>400 (lần 2)</t>
-  </si>
-  <si>
-    <t>Retest</t>
+    <t>200 OK</t>
+  </si>
+  <si>
+    <t>Tỉnh trạng(RECHECK)</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
+    <t>THANH</t>
+  </si>
+  <si>
+    <t>THÙY</t>
   </si>
 </sst>
 </file>
@@ -882,26 +900,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.44140625" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="29.21875" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="17.77734375" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.5" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="29.1640625" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="16.83203125" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="16.5" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="17.83203125" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="40" customWidth="1"/>
     <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" customWidth="1"/>
-    <col min="14" max="14" width="44.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -939,13 +957,16 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>133</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>13</v>
       </c>
@@ -982,14 +1003,14 @@
       <c r="L2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="13" t="s">
+      <c r="M2" s="13" t="s">
         <v>25</v>
       </c>
+      <c r="N2" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
@@ -1026,14 +1047,14 @@
       <c r="L3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="N3" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="1:14" ht="53.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>34</v>
       </c>
@@ -1061,34 +1082,37 @@
       <c r="I4" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="13">
-        <v>400</v>
+      <c r="J4" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N4" s="14" t="s">
         <v>41</v>
       </c>
+      <c r="M4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
+        <v>135</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" ht="53.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="57" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>30</v>
@@ -1105,34 +1129,37 @@
       <c r="I5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="13">
-        <v>400</v>
+      <c r="J5" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="60" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>17</v>
@@ -1141,45 +1168,48 @@
         <v>18</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>53</v>
+        <v>41</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>31</v>
@@ -1191,10 +1221,10 @@
         <v>20</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>23</v>
@@ -1202,28 +1232,28 @@
       <c r="L7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>125</v>
+      <c r="M7" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>18</v>
@@ -1235,10 +1265,10 @@
         <v>20</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>23</v>
@@ -1246,28 +1276,28 @@
       <c r="L8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>64</v>
+      <c r="M8" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="45" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>18</v>
@@ -1279,10 +1309,10 @@
         <v>20</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>23</v>
@@ -1290,43 +1320,43 @@
       <c r="L9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>70</v>
+      <c r="M9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="45" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>23</v>
@@ -1334,43 +1364,43 @@
       <c r="L10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>127</v>
+      <c r="M10" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="45" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C11" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>75</v>
-      </c>
       <c r="H11" s="10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>23</v>
@@ -1378,43 +1408,43 @@
       <c r="L11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>82</v>
+      <c r="M11" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="60" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>23</v>
@@ -1422,43 +1452,43 @@
       <c r="L12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>90</v>
+      <c r="M12" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>23</v>
@@ -1466,85 +1496,88 @@
       <c r="L13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>97</v>
+      <c r="M13" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="45" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>95</v>
-      </c>
       <c r="I14" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J14" s="8">
-        <v>400</v>
+        <v>105</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>132</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>103</v>
+        <v>131</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="69" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="75" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>23</v>
@@ -1552,41 +1585,41 @@
       <c r="L15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>109</v>
+      <c r="M15" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H16" s="8"/>
       <c r="I16" s="8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>23</v>
@@ -1594,15 +1627,15 @@
       <c r="L16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>114</v>
+      <c r="M16" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
